--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f1713fb79de40b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b544e99c7e749e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4f3417c729ba424b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf86f31afeafa482e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d65a001ff074f37"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84e128cd75dc46cc"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4b544e99c7e749e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8132850a12d74ac4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf86f31afeafa482e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca7b92f6c10c4ecc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84e128cd75dc46cc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce1b2ad98a5410a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8132850a12d74ac4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf072c6d52cbd421d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca7b92f6c10c4ecc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3cf415fcd984a27"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce1b2ad98a5410a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra217ebc6feb94d69"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf072c6d52cbd421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83815695633742ed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3cf415fcd984a27"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1bad3f100574fcf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra217ebc6feb94d69"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14ed138130f4f39"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R83815695633742ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37c53215575e4a00"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1bad3f100574fcf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree751f139e004cc3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf14ed138130f4f39"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503650834a1f4926"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R37c53215575e4a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbbc31a8e8c954e8c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree751f139e004cc3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R852174df719b4e79"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R503650834a1f4926"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea62763a85a4986"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbbc31a8e8c954e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6747591ce31d4abe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R852174df719b4e79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd2b2809385a40ec"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ea62763a85a4986"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13e7dd2ef46d43a0"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6747591ce31d4abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f52f273fdc44b20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdd2b2809385a40ec"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab2c6168a0344b75"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13e7dd2ef46d43a0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a429894bb0a45fb"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4f52f273fdc44b20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc3b9cc5100144e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab2c6168a0344b75"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redc8bbf0257c44ae"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a429894bb0a45fb"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21174cb8037a4eef"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc3b9cc5100144e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8efef92b6a44411a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redc8bbf0257c44ae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f2d59e4826142dd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21174cb8037a4eef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R245c6c86a1664c70"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8efef92b6a44411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf3b8fa734053406d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f2d59e4826142dd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R811325a15aab4af7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R245c6c86a1664c70"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R476666c3515c40d6"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf3b8fa734053406d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R078dadeaf7154184"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R811325a15aab4af7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0569b585922045d3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R476666c3515c40d6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05edd02d0fff42e6"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R078dadeaf7154184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cd3c328351943d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0569b585922045d3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re46f909a0999461a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05edd02d0fff42e6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R960a04199e454721"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6cd3c328351943d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f6573665d604792"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re46f909a0999461a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85904726e712425f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R960a04199e454721"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re21c30f111fc4979"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartPie/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f6573665d604792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5fd33468f3ad4b1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -129,7 +129,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R85904726e712425f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1028e5e613c94774"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -174,6 +174,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re21c30f111fc4979"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4418c140e1cd49f9"/>
 </x:worksheet>
 </file>